--- a/artfynd/A 20496-2025 artfynd.xlsx
+++ b/artfynd/A 20496-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56220108</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540170.1358977023</v>
+        <v>540170</v>
       </c>
       <c r="R2" t="n">
-        <v>6979098.079562166</v>
+        <v>6979098</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56220110</v>
+        <v>56220109</v>
       </c>
       <c r="B3" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540172.5588803622</v>
+        <v>540131</v>
       </c>
       <c r="R3" t="n">
-        <v>6979234.717238726</v>
+        <v>6979194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2015-06-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-06-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56220111</v>
+        <v>56220110</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540147.332349861</v>
+        <v>540173</v>
       </c>
       <c r="R4" t="n">
-        <v>6979246.701399412</v>
+        <v>6979235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2015-06-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56220109</v>
+        <v>56220112</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540131.1070007161</v>
+        <v>540176</v>
       </c>
       <c r="R5" t="n">
-        <v>6979194.136472838</v>
+        <v>6979235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2015-06-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-06-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56220112</v>
+        <v>132445328</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,37 +1090,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramsjömossan, Jmt</t>
+          <t>Krokflodalen, Krokflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540176.2062094327</v>
+        <v>540177</v>
       </c>
       <c r="R6" t="n">
-        <v>6979234.76211415</v>
+        <v>6979126</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1144,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-06-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,26 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Matilda Ågevall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132445328</v>
+        <v>132445527</v>
       </c>
       <c r="B7" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540177</v>
+        <v>540088</v>
       </c>
       <c r="R7" t="n">
-        <v>6979126</v>
+        <v>6979124</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1362,56 +1293,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132445788</v>
+        <v>132445556</v>
       </c>
       <c r="B8" t="n">
-        <v>58062</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Krokflodalen, Krokflodalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540181</v>
+        <v>540093</v>
       </c>
       <c r="R8" t="n">
-        <v>6979179</v>
+        <v>6979141</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1363,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1373,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,7 +1403,7 @@
         <v>132445905</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132445866</v>
+        <v>132446337</v>
       </c>
       <c r="B10" t="n">
-        <v>58119</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,13 +1542,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540185</v>
+        <v>540211</v>
       </c>
       <c r="R10" t="n">
-        <v>6979191</v>
+        <v>6979270</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1577,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1587,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,6 +1611,436 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132446674</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Krokflodalen, Krokflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>540280</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6979274</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132445866</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Krokflodalen, Krokflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>540185</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6979191</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132445788</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Krokflodalen, Krokflodalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>540181</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6979179</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>56220111</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ramsjömossan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>540147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6979247</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-06-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-06-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20496-2025 artfynd.xlsx
+++ b/artfynd/A 20496-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220108</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220109</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220110</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445527</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445905</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446337</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446674</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445866</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132445788</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,8 +2106,28 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220111</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>